--- a/04-northbridge-cloudworks-grc-program/02-nist-csf-gap-assessment/artifacts/Northbridge-NIST-CSF-2.0-Gap-Assessment.xlsx
+++ b/04-northbridge-cloudworks-grc-program/02-nist-csf-gap-assessment/artifacts/Northbridge-NIST-CSF-2.0-Gap-Assessment.xlsx
@@ -12,7 +12,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard'!$A$1:$H$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'CSF Assessment'!$A$1:$M$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Roadmap'!$A$1:$H$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'References'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'References'!$A$1:$C$19</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B8" s="33" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="D8" s="31" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3277,6 +3277,23 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>Scenario dates and rating definitions</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>Fictional assessment assumptions; see shared company profile</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>../../00-company-profile/Northbridge-Company-and-GRC-Scope.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
